--- a/partner_results/dik/ClassMissingGermanLabel_dik.xlsx
+++ b/partner_results/dik/ClassMissingGermanLabel_dik.xlsx
@@ -446,12 +446,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>organodiyl group [dik]</t>
+          <t>hydrocarbylene group [dik]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>organic divalent group [chebi]</t>
+          <t>organodiyl group [chebi]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -459,18 +459,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>hydrocarbylene group [dik]</t>
+          <t>organic divalent group [dik]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>organodiyl group [chebi]</t>
+          <t>organic group [chebi]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -478,18 +482,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>organic divalent group [dik]</t>
+          <t>organodiyl group [dik]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>organic group [chebi]</t>
+          <t>organic divalent group [chebi]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -497,7 +505,11 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -516,7 +528,11 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr"/>
     </row>
   </sheetData>
